--- a/Documentation/Week 11/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 11/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 11/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="467" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAB59483-7F0A-4E6C-B05C-6AAFEE4DDDCA}"/>
+  <xr:revisionPtr revIDLastSave="479" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7C8A4A5-5C2F-48E8-8AE7-5BAAECB4CE94}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="17280" windowHeight="10008" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="47">
   <si>
     <t>Wk</t>
   </si>
@@ -186,6 +186,9 @@
   </si>
   <si>
     <t>Testing and debugging</t>
+  </si>
+  <si>
+    <t>Cleanup project (coding and commenting)</t>
   </si>
 </sst>
 </file>
@@ -380,7 +383,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -420,6 +423,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -440,20 +451,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -539,6 +545,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -879,36 +889,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="13"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="15"/>
     </row>
     <row r="2" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="16" t="s">
+      <c r="C2" s="12"/>
+      <c r="D2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="17"/>
+      <c r="E2" s="12"/>
       <c r="F2" s="18" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="16" t="s">
         <v>6</v>
       </c>
     </row>
@@ -928,7 +938,7 @@
       </c>
       <c r="F3" s="19"/>
       <c r="G3" s="10"/>
-      <c r="H3" s="15"/>
+      <c r="H3" s="17"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -1798,14 +1808,14 @@
       <c r="A31" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="16" t="s">
+      <c r="C31" s="12"/>
+      <c r="D31" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="17"/>
+      <c r="E31" s="12"/>
       <c r="F31" s="8" t="s">
         <v>5</v>
       </c>
@@ -2870,14 +2880,14 @@
       <c r="A65" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="16" t="s">
+      <c r="B65" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="17"/>
-      <c r="D65" s="16" t="s">
+      <c r="C65" s="12"/>
+      <c r="D65" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="17"/>
+      <c r="E65" s="12"/>
       <c r="F65" s="8" t="s">
         <v>5</v>
       </c>
@@ -2915,31 +2925,67 @@
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="G67" s="6" t="str">
+      <c r="A67" s="1">
+        <v>11</v>
+      </c>
+      <c r="B67" s="20">
+        <v>44842</v>
+      </c>
+      <c r="C67" s="7">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D67" s="20">
+        <v>44842</v>
+      </c>
+      <c r="E67" s="7">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G67" s="6">
         <f t="shared" ref="G67:G98" si="6">IF(I67&gt;0,I67,IF(I67=0, " ", "ERROR"))</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H67" s="1" t="str">
+        <v>7.2499999998835847</v>
+      </c>
+      <c r="H67" s="1">
         <f>IF(AND(G67&lt;&gt;" ",G67&lt;&gt;"ERROR",H64&lt;&gt;" ", H64&lt;&gt;"ERROR"),G67+H64," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>74.249999999650754</v>
       </c>
       <c r="I67" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>7.2499999998835847</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="G68" s="6" t="str">
+      <c r="A68" s="1">
+        <v>11</v>
+      </c>
+      <c r="B68" s="20">
+        <v>44842</v>
+      </c>
+      <c r="C68" s="7">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="D68" s="20">
+        <v>44842</v>
+      </c>
+      <c r="E68" s="7">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G68" s="6">
         <f t="shared" si="6"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H68" s="1" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="H68" s="1">
         <f t="shared" ref="H68:H98" si="7">IF(AND(G68&lt;&gt;" ",G68&lt;&gt;"ERROR",H67&lt;&gt;" ", H67&lt;&gt;"ERROR"),G68+H67," ")</f>
-        <v xml:space="preserve"> </v>
+        <v>74.999999999650754</v>
       </c>
       <c r="I68" s="1">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
@@ -3366,14 +3412,14 @@
       <c r="A99" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B99" s="16" t="s">
+      <c r="B99" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="17"/>
-      <c r="D99" s="16" t="s">
+      <c r="C99" s="12"/>
+      <c r="D99" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E99" s="17"/>
+      <c r="E99" s="12"/>
       <c r="F99" s="8" t="s">
         <v>5</v>
       </c>
@@ -3860,18 +3906,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -3885,6 +3919,18 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
